--- a/out/Attention-MambaAMT_repeat_5_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.534689842160187</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.534689842160187</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-0.0003831747714354424</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>4.417439201795405</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC40" t="n">
-        <v>-6.49797534198733e-05</v>
+        <v>8.84170696738707</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.08379074020421616</v>
+        <v>0.6624147135143021</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.08385571995763609</v>
+        <v>5.743168381592731</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.8282339277018177</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.368300414422388</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.08391460247837437</v>
+        <v>6.737326719558172</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.09830024392166083</v>
+        <v>1.187269244867683</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.134689842160187</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.1129220137044464</v>
+        <v>8.284099016259512</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1352398274766206</v>
+        <v>1.270142917971595</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2851132725358678</v>
+        <v>9.637204499322685</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1581020624072968</v>
+        <v>1.346095483887721</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4660905812190508</v>
+        <v>11.05934944137235</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.07070559030699432</v>
+        <v>0.6074678561519354</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4492572067618005</v>
+        <v>10.92707092580551</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03403509395928864</v>
+        <v>0.2933798524291984</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.446561142010486</v>
+        <v>10.90588510393658</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01613907951683861</v>
+        <v>0.1397867652082984</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4447744978532814</v>
+        <v>10.89184579764745</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004442473662291642</v>
+        <v>0.04141784345315883</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.437504305012824</v>
+        <v>10.83474582002921</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003070007873877422</v>
+        <v>0.02739587847371611</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4391998803960621</v>
+        <v>10.84809906925257</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001573694471264434</v>
+        <v>0.0140212801990365</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4392752101228186</v>
+        <v>10.84872514763043</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0008049425027950786</v>
+        <v>0.007169481053679173</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4393103616093341</v>
+        <v>10.8490354929855</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002870188887074269</v>
+        <v>0.002692537844840163</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4390778714035256</v>
+        <v>10.84724464476192</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001564729249908783</v>
+        <v>0.00146516065147483</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4391036069404925</v>
+        <v>10.84748092549706</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.195960424264547e-05</v>
+        <v>0.0007031043859474707</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4390916163485532</v>
+        <v>10.84742104400088</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.460616585560791e-05</v>
+        <v>0.0004328600272585929</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4391081456524434</v>
+        <v>10.84758431310657</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.063953424346452e-05</v>
+        <v>0.0002245493221192557</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4391057022928821</v>
+        <v>10.84759931279655</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.395902747928427e-06</v>
+        <v>0.0001058993375171547</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4390998062075362</v>
+        <v>10.84758741814152</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.158324102806951e-06</v>
+        <v>6.663219715471185e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.439099001185132</v>
+        <v>10.84761373484457</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-7.922409131858519e-07</v>
+        <v>2.763711577382715e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4390930861483514</v>
+        <v>10.8476023295871</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.168604696895391e-06</v>
+        <v>9.411168204796322e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4390875380201305</v>
+        <v>10.84759349268955</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>2.788397616378431e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.439082703385812</v>
+        <v>10.84758965024933</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-2.093548687745288e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4390825594019045</v>
+        <v>10.84758363882274</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-3.107779831880603e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4390825366676031</v>
+        <v>10.8475785455806</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4390828549478198</v>
+        <v>10.84757418060663</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4390839461942767</v>
+        <v>10.84757527185309</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4390832565871407</v>
+        <v>10.84757458224595</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4390832868995425</v>
+        <v>10.84757461255836</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4390830974470323</v>
+        <v>10.84757442310585</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4390831504937352</v>
+        <v>10.84757447615255</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4390832035404381</v>
+        <v>10.84757452919925</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.439083165649936</v>
+        <v>10.84757449130875</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4390830368222294</v>
+        <v>10.84757436248104</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4390828928383219</v>
+        <v>10.84757421849713</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4390827336982135</v>
+        <v>10.84757405935703</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4390827867449164</v>
+        <v>10.84757411240373</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4390827336982135</v>
+        <v>10.84757405935703</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4390827336982135</v>
+        <v>10.84757405935703</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4390825518238039</v>
+        <v>10.84757387748262</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4390827185420126</v>
+        <v>10.84757404420083</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.439082915572623</v>
+        <v>10.84757424123144</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4390827564325147</v>
+        <v>10.84757408209133</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4390827943230167</v>
+        <v>10.84757411998183</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4390829913536268</v>
+        <v>10.84757431701244</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4390829686193257</v>
+        <v>10.84757429427814</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4390828170573178</v>
+        <v>10.84757414271613</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4390827412763138</v>
+        <v>10.84757406693513</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.439082839791619</v>
+        <v>10.84757416545043</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4390828473697193</v>
+        <v>10.84757417302853</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4390831126032332</v>
+        <v>10.84757443826205</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4390828170573178</v>
+        <v>10.84757414271613</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4390830595565305</v>
+        <v>10.84757438521534</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4390831429156349</v>
+        <v>10.84757446857445</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4390829761974262</v>
+        <v>10.84757430185624</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.439083165649936</v>
+        <v>10.84757449130875</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4390828170573178</v>
+        <v>10.84757414271613</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4390826124486071</v>
+        <v>10.84757393810742</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4390827261201132</v>
+        <v>10.84757405177893</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4390827412763138</v>
+        <v>10.84757406693513</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4390825063552016</v>
+        <v>10.84757383201402</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4390825669800048</v>
+        <v>10.84757389263882</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4390824381522981</v>
+        <v>10.84757376381111</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4390825745581051</v>
+        <v>10.84757390021692</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4390827488544143</v>
+        <v>10.84757407451323</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4390828928383219</v>
+        <v>10.84757421849713</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4390827261201132</v>
+        <v>10.84757405177893</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4390827185420126</v>
+        <v>10.84757404420083</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4390824305741975</v>
+        <v>10.84757375623301</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4390824457303984</v>
+        <v>10.84757377138921</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4390826730734103</v>
+        <v>10.84757399873222</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4390826579172095</v>
+        <v>10.84757398357602</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.439082764010615</v>
+        <v>10.84757408966943</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4390824911990007</v>
+        <v>10.84757381685781</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4390825897143059</v>
+        <v>10.84757391537312</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4390827412763138</v>
+        <v>10.84757406693513</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4390827564325147</v>
+        <v>10.84757408209133</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4390827336982135</v>
+        <v>10.84757405935703</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4390828170573178</v>
+        <v>10.84757414271613</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.439082915572623</v>
+        <v>10.84757424123144</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4390827488544143</v>
+        <v>10.84757407451323</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4390827336982135</v>
+        <v>10.84757405935703</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.439082703385812</v>
+        <v>10.84757402904462</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4390826882296112</v>
+        <v>10.84757401388842</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4390827261201132</v>
+        <v>10.84757405177893</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4390827412763138</v>
+        <v>10.84757406693513</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4390827336982135</v>
+        <v>10.84757405935703</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279057</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.09099177447209424</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.09099177447209424</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.534689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.368300414422388</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.534689842160187</v>
+        <v>0.5545324045481114</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.534689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.134689842160187</v>
+        <v>1.218073034624129</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.368300414422388</v>
+        <v>0.5545324045481114</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.368300414422388</v>
+        <v>0.5545324045481114</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.534689842160187</v>
+        <v>0.5545324045481114</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.534689842160187</v>
+        <v>0.5545324045481114</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.534689842160187</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,17 +31942,17 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC39" t="n">
-        <v>0</v>
+        <v>-4.108687890111469e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,21 +32733,21 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0</v>
+        <v>0.4736709566433745</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC40" t="n">
-        <v>-6.49797534198733e-05</v>
+        <v>0.9480742746583612</v>
       </c>
     </row>
     <row r="41">
@@ -33528,21 +33528,21 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>-0.08379074020421616</v>
+        <v>0.07102907288852793</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC41" t="n">
-        <v>-0.08385571995763609</v>
+        <v>0.615825626121385</v>
       </c>
     </row>
     <row r="42">
@@ -34323,21 +34323,21 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0</v>
+        <v>0.08880945247635112</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279057</v>
       </c>
       <c r="JC42" t="n">
-        <v>-0.08391460247837437</v>
+        <v>0.7224268063005861</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.09830024392166083</v>
+        <v>0.1273080916296755</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.1129220137044464</v>
+        <v>0.888283542771129</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1352398274766206</v>
+        <v>0.136194440884327</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2851132725358678</v>
+        <v>1.03337382477258</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1581020624072968</v>
+        <v>0.1443386560764225</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4660905812190508</v>
+        <v>1.185867001873032</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.07070559030699432</v>
+        <v>0.06513735096514853</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4492572067618005</v>
+        <v>1.171683102877164</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03403509395928864</v>
+        <v>0.03145836331314331</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.446561142010486</v>
+        <v>1.169411401954548</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01613907951683861</v>
+        <v>0.01498852521192327</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.134689842160187</v>
+        <v>0.09099177447209421</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4447744978532814</v>
+        <v>1.167905555095138</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004442473662291642</v>
+        <v>0.004437486756411302</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.368300414422388</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.437504305012824</v>
+        <v>1.161779230524965</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003070007873877422</v>
+        <v>0.002933535433781865</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.134689842160187</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4391998803960621</v>
+        <v>1.163206959519651</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001573694471264434</v>
+        <v>0.001498483419440742</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4392752101228186</v>
+        <v>1.163269627835249</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0008049425027950786</v>
+        <v>0.000764089873019628</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4393103616093341</v>
+        <v>1.163298452517391</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002870188887074269</v>
+        <v>0.0002841300383639007</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4390778714035256</v>
+        <v>1.163101789976159</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001564729249908783</v>
+        <v>0.0001525761416563931</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279059</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4391036069404925</v>
+        <v>1.163122719357744</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.195960424264547e-05</v>
+        <v>7.129407525359953e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.534689842160187</v>
+        <v>0.5545324045481114</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4390916163485532</v>
+        <v>1.163111806199907</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.460616585560791e-05</v>
+        <v>4.222984563688194e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4391081456524434</v>
+        <v>1.163124936140026</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.063953424346452e-05</v>
+        <v>1.970485977965084e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4391057022928821</v>
+        <v>1.163122088573028</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.395902747928427e-06</v>
+        <v>6.989117569422133e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4390998062075362</v>
+        <v>1.163116346481933</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.158324102806951e-06</v>
+        <v>2.674878266576269e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.439099001185132</v>
+        <v>1.163114701842974</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-7.922409131858519e-07</v>
+        <v>-1.503166167089948e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.09099177447209424</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4390930861483514</v>
+        <v>1.163109015565389</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.168604696895391e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4390875380201305</v>
+        <v>1.163103605095471</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.001043275021943e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.439082703385812</v>
+        <v>1.163098770461153</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4390825594019045</v>
+        <v>1.163098626477245</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279057</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4390825366676031</v>
+        <v>1.163098603742944</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.534689842160187</v>
+        <v>0.5545324045481114</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4390828549478198</v>
+        <v>1.16309892202316</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4390839461942767</v>
+        <v>1.163100013269618</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4390832565871407</v>
+        <v>1.163099323662482</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4390832868995425</v>
+        <v>1.163099353974883</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4390830974470323</v>
+        <v>1.163099164522373</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4390831504937352</v>
+        <v>1.163099217569076</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4390832035404381</v>
+        <v>1.163099270615779</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.439083165649936</v>
+        <v>1.163099232725277</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4390830368222294</v>
+        <v>1.16309910389757</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4390828928383219</v>
+        <v>1.163098959913663</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4390827336982135</v>
+        <v>1.163098800773554</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4390827867449164</v>
+        <v>1.163098853820257</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4390827336982135</v>
+        <v>1.163098800773554</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4390827336982135</v>
+        <v>1.163098800773554</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4390825518238039</v>
+        <v>1.163098618899145</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4390827185420126</v>
+        <v>1.163098785617353</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.439082915572623</v>
+        <v>1.163098982647964</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4390827564325147</v>
+        <v>1.163098823507856</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.368300414422388</v>
+        <v>0.09099177447209431</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4390827943230167</v>
+        <v>1.163098861398357</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.134689842160187</v>
+        <v>0.09099177447209428</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4390829913536268</v>
+        <v>1.163099058428968</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.09099177447209428</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4390829686193257</v>
+        <v>1.163099035694667</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.572548855603923</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4390828170573178</v>
+        <v>1.163098884132659</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.572548855603923</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4390827412763138</v>
+        <v>1.163098808351654</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.439082839791619</v>
+        <v>1.16309890686696</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4390828473697193</v>
+        <v>1.16309891444506</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4390831126032332</v>
+        <v>1.163099179678574</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.1090082255279057</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4390828170573178</v>
+        <v>1.163098884132659</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.134689842160187</v>
+        <v>0.09099177447209428</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4390830595565305</v>
+        <v>1.163099126631871</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4390831429156349</v>
+        <v>1.163099209990975</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.134689842160187</v>
+        <v>0.09099177447209428</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4390829761974262</v>
+        <v>1.163099043272767</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.09099177447209428</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.439083165649936</v>
+        <v>1.163099232725277</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.572548855603923</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4390828170573178</v>
+        <v>1.163098884132659</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4390826124486071</v>
+        <v>1.163098679523948</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4390827261201132</v>
+        <v>1.163098793195454</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4390827412763138</v>
+        <v>1.163098808351654</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4390825063552016</v>
+        <v>1.163098573430542</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4390825669800048</v>
+        <v>1.163098634055345</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4390824381522981</v>
+        <v>1.163098505227639</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4390825745581051</v>
+        <v>1.163098641633446</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4390827488544143</v>
+        <v>1.163098815929755</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4390828928383219</v>
+        <v>1.163098959913663</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4390827261201132</v>
+        <v>1.163098793195454</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.368300414422388</v>
+        <v>0.09099177447209431</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4390827185420126</v>
+        <v>1.163098785617353</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4390824305741975</v>
+        <v>1.163098497649538</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4390824457303984</v>
+        <v>1.163098512805739</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>2.134689842160187</v>
+        <v>1.418073034624129</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4390826730734103</v>
+        <v>1.163098740148751</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4390826579172095</v>
+        <v>1.16309872499255</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7683004144223875</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.439082764010615</v>
+        <v>1.163098831085956</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4390824911990007</v>
+        <v>1.163098558274342</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.134689842160187</v>
+        <v>0.7545324045481114</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4390825897143059</v>
+        <v>1.163098656789647</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7683004144223875</v>
+        <v>-0.1090082255279058</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4390827412763138</v>
+        <v>1.163098808351654</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4390827564325147</v>
+        <v>1.163098823507856</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4390827336982135</v>
+        <v>1.163098800773554</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4390828170573178</v>
+        <v>1.163098884132659</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.439082915572623</v>
+        <v>1.163098982647964</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4390827488544143</v>
+        <v>1.163098815929755</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4390827336982135</v>
+        <v>1.163098800773554</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.439082703385812</v>
+        <v>1.163098770461153</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4390826882296112</v>
+        <v>1.163098755304952</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4390827261201132</v>
+        <v>1.163098793195454</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4390827412763138</v>
+        <v>1.163098808351654</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.970767248321669e-06</v>
+        <v>-3.857095742388521e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.368300414422388</v>
+        <v>-0.7725488556039231</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4390827336982135</v>
+        <v>1.163098800773554</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.004285328090190887</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.00397365540266037</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.007900342345237732</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01056699454784393</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.008642159402370453</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.008066929876804352</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.002729408442974091</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001230143010616302</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001592516899108887</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0034775510430336</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1090082255279057</v>
+        <v>0.16</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.003055758774280548</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.004971206188201904</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.418073034624129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.003112912178039551</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001583211123943329</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.09099177447209424</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.004218794405460358</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.09099177447209424</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.005944602191448212</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01243793219327927</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.418073034624129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01037091761827469</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.418073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01335887610912323</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.418073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01735714450478554</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.418073034624129</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.007057018578052521</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.418073034624129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001181416213512421</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7545324045481114</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.006994009017944336</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.7545324045481114</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001757867634296417</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5545324045481114</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.004338338971138</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.00483250617980957</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.218073034624129</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.007314182817935944</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.418073034624129</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.006736323237419128</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7545324045481114</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0127173438668251</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5545324045481114</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002473227679729462</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.001317627727985382</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5545324045481114</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0002221688628196716</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.5545324045481114</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001812905073165894</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5545324045481114</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0005739405751228333</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.005681522190570831</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.03404548764228821</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.01250436156988144</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.02052085846662521</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-4.108687890111469e-05</v>
+        <v>-4.509415504976641e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.4736709566433745</v>
+        <v>0.5198689322694642</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.007188767194747925</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>0.9480742746583612</v>
+        <v>1.040541639643568</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.07102907288852793</v>
+        <v>0.07795666541246331</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.02114901691675186</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.615825626121385</v>
+        <v>0.6758881964905513</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.08880945247635112</v>
+        <v>0.09747125396475941</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.01402246206998825</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1090082255279057</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>0.7224268063005861</v>
+        <v>0.7928863736962299</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1273080916296755</v>
+        <v>0.1397244176357254</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.00674053281545639</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>0.888283542771129</v>
+        <v>0.9749192879497705</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.136194440884327</v>
+        <v>0.1494777983474992</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.02003611624240875</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.418073034624129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.03337382477258</v>
+        <v>1.13416055928488</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1443386560764225</v>
+        <v>0.1584163376026855</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.03379633277654648</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.418073034624129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.185867001873032</v>
+        <v>1.301526747126208</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.06513735096514853</v>
+        <v>0.07148968094764276</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.051457479596138</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.171683102877164</v>
+        <v>1.285959460807164</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03145836331314331</v>
+        <v>0.03452624835165521</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.02201147377490997</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.169411401954548</v>
+        <v>1.283466173415764</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01498852521192327</v>
+        <v>0.01645133806585069</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.03519127517938614</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.09099177447209421</v>
+        <v>0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.167905555095138</v>
+        <v>1.281813899478887</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004437486756411302</v>
+        <v>0.004870545655138998</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.02259228378534317</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7545324045481114</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.161779230524965</v>
+        <v>1.275090360746266</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.002933535433781865</v>
+        <v>0.003219987366809996</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.002089746296405792</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.163206959519651</v>
+        <v>1.276657988790431</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001498483419440742</v>
+        <v>0.001646076687055998</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.003937013447284698</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.163269627835249</v>
+        <v>1.276727274971985</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.000764089873019628</v>
+        <v>0.0008395895333291463</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.001941725611686707</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.163298452517391</v>
+        <v>1.276759395173868</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002841300383639007</v>
+        <v>0.0003121347802996712</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.007118090987205505</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.163101789976159</v>
+        <v>1.276544192681943</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001525761416563931</v>
+        <v>0.0001682512552243065</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.007870502769947052</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1090082255279059</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.163122719357744</v>
+        <v>1.276567626438608</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.129407525359953e-05</v>
+        <v>7.844664480862448e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.002889782190322876</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5545324045481114</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.163111806199907</v>
+        <v>1.276556158922224</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.222984563688194e-05</v>
+        <v>4.61656661066221e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.005784735083580017</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.163124936140026</v>
+        <v>1.276570989143195</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.970485977965084e-05</v>
+        <v>2.176359809462174e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.02165442705154419</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.163122088573028</v>
+        <v>1.276568366414217</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.989117569422133e-06</v>
+        <v>7.988210700207309e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.04759246483445168</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.163116346481933</v>
+        <v>1.276562532169796</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.674878266576269e-06</v>
+        <v>3.954024644338981e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01266554743051529</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.163114701842974</v>
+        <v>1.276561446757677</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01840582489967346</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.09099177447209424</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.163109015565389</v>
+        <v>1.276555646808586</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.970630842514548e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.00505463033914566</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.163103605095471</v>
+        <v>1.276550098680365</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.002400152385234833</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.163098770461153</v>
+        <v>1.276545264046046</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.007093802094459534</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.163098626477245</v>
+        <v>1.276545120062139</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01151224225759506</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1090082255279057</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.163098603742944</v>
+        <v>1.276545097327838</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.03344002366065979</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5545324045481114</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.16309892202316</v>
+        <v>1.276545415608054</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0697900727391243</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.418073034624129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.163100013269618</v>
+        <v>1.276546506854511</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.03714185208082199</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.418073034624129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.163099323662482</v>
+        <v>1.276545817247375</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01079940795898438</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.163099353974883</v>
+        <v>1.276545847559777</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.006618477404117584</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.163099164522373</v>
+        <v>1.276545658107267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.004451148211956024</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7545324045481114</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.163099217569076</v>
+        <v>1.27654571115397</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.00372873991727829</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.418073034624129</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.163099270615779</v>
+        <v>1.276545764200673</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.0005704537034034729</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7545324045481114</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.163099232725277</v>
+        <v>1.27654572631017</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001692131161689758</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.16309910389757</v>
+        <v>1.276545597482464</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.006315030157566071</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.163098959913663</v>
+        <v>1.276545453498556</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.00677189975976944</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.163098800773554</v>
+        <v>1.276545294358448</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006034255027770996</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.163098853820257</v>
+        <v>1.27654534740515</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001685440540313721</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.163098800773554</v>
+        <v>1.276545294358448</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.007391557097434998</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.163098800773554</v>
+        <v>1.276545294358448</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01267054677009583</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.163098618899145</v>
+        <v>1.276545112484038</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.007742762565612793</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.163098785617353</v>
+        <v>1.276545279202247</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-8.195638656616211e-05</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.163098982647964</v>
+        <v>1.276545476232857</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.007251277565956116</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.163098823507856</v>
+        <v>1.276545317092749</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.009008504450321198</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.09099177447209431</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.163098861398357</v>
+        <v>1.276545354983251</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.005798950791358948</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.09099177447209428</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.163099058428968</v>
+        <v>1.276545552013862</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01065108180046082</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.09099177447209428</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.163099035694667</v>
+        <v>1.27654552927956</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.008314087986946106</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.572548855603923</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.163098884132659</v>
+        <v>1.276545377717552</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003522224724292755</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.572548855603923</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.163098808351654</v>
+        <v>1.276545301936548</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.01121667772531509</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.16309890686696</v>
+        <v>1.276545400451853</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.006311468780040741</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.16309891444506</v>
+        <v>1.276545408029954</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.007848687469959259</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.163099179678574</v>
+        <v>1.276545673263468</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01210589706897736</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1090082255279057</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.163098884132659</v>
+        <v>1.276545377717552</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.003393739461898804</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.09099177447209428</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.163099126631871</v>
+        <v>1.276545620216765</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01999001204967499</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.163099209990975</v>
+        <v>1.276545703575869</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01940780878067017</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.09099177447209428</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.163099043272767</v>
+        <v>1.27654553685766</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.006941743195056915</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.09099177447209428</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.163099232725277</v>
+        <v>1.27654572631017</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.02060864120721817</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.572548855603923</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.163098884132659</v>
+        <v>1.276545377717552</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01072665303945541</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.163098679523948</v>
+        <v>1.276545173108842</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.00592823326587677</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.163098793195454</v>
+        <v>1.276545286780348</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.009531870484352112</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.163098808351654</v>
+        <v>1.276545301936548</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.006987296044826508</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.163098573430542</v>
+        <v>1.276545067015436</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.003759913146495819</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.163098634055345</v>
+        <v>1.276545127640239</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.006394147872924805</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.163098505227639</v>
+        <v>1.276544998812533</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.006324902176856995</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7725488556039231</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.163098641633446</v>
+        <v>1.276545135218339</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01214029639959335</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.163098815929755</v>
+        <v>1.276545309514649</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.007908739149570465</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.163098959913663</v>
+        <v>1.276545453498556</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01090014725923538</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.163098793195454</v>
+        <v>1.276545286780348</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01058318465948105</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.09099177447209431</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.163098785617353</v>
+        <v>1.276545279202247</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0002454221248626709</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.163098497649538</v>
+        <v>1.276544991234432</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.007930725812911987</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.418073034624129</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.163098512805739</v>
+        <v>1.276545006390633</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.001981161534786224</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.418073034624129</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.163098740148751</v>
+        <v>1.276545233733645</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.0024590864777565</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.16309872499255</v>
+        <v>1.276545218577444</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002010010182857513</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.163098831085956</v>
+        <v>1.276545324670849</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.005425527691841125</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.163098558274342</v>
+        <v>1.276545051859235</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.002269551157951355</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7545324045481114</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.163098656789647</v>
+        <v>1.276545150374541</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.00172201544046402</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1090082255279058</v>
+        <v>-0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.163098808351654</v>
+        <v>1.276545301936548</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002880237996578217</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.163098823507856</v>
+        <v>1.276545317092749</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.004071332514286041</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.163098800773554</v>
+        <v>1.276545294358448</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.00215081125497818</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.163098884132659</v>
+        <v>1.276545377717552</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003346368670463562</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.163098982647964</v>
+        <v>1.276545476232857</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.0008477345108985901</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.163098815929755</v>
+        <v>1.276545309514649</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.002998225390911102</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.163098800773554</v>
+        <v>1.276545294358448</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003610588610172272</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.163098770461153</v>
+        <v>1.276545264046046</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.004844851791858673</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.163098755304952</v>
+        <v>1.276545248889845</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.00374198704957962</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.163098793195454</v>
+        <v>1.276545286780348</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.009090498089790344</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.163098808351654</v>
+        <v>1.276545301936548</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01480572670698166</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7725488556039231</v>
+        <v>-1</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.163098800773554</v>
+        <v>1.276545294358448</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000007.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000007.xlsx
@@ -39104,7 +39104,7 @@
         <v>0.03519127517938614</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.3</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC48" t="n">
         <v>1.281813899478887</v>
@@ -39899,7 +39899,7 @@
         <v>-0.02259228378534317</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>1.275090360746266</v>
@@ -40694,7 +40694,7 @@
         <v>0.002089746296405792</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>1.276657988790431</v>
@@ -41489,7 +41489,7 @@
         <v>-0.003937013447284698</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>1.276727274971985</v>
@@ -42284,7 +42284,7 @@
         <v>-0.001941725611686707</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>1.276759395173868</v>
@@ -44669,7 +44669,7 @@
         <v>0.002889782190322876</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC55" t="n">
         <v>1.276556158922224</v>
